--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N7_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.34277365242677</v>
+        <v>11.75570071851935</v>
       </c>
       <c r="D2" t="n">
-        <v>73.49768236885683</v>
+        <v>11.94337338493924</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
